--- a/remina_roi_sample.xlsx
+++ b/remina_roi_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_38DFA0D6DAB69FA65B9544D91F3F068DF6D366F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF3E20D-2AC2-4BB6-88CA-DB17F66E6E44}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_38DFA0D6DAB69FA65B9544D91F3F068DF6D366F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,21 +12,10 @@
     <sheet name="Detailed Model" sheetId="2" r:id="rId2"/>
     <sheet name="KPI Dashboard" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -1647,7 +1636,7 @@
       </c>
       <c r="C19" s="27">
         <f>ROUND(C4*0.4,0)*C9*12</f>
-        <v>19.200000000000003</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="18" customHeight="1">
@@ -1656,7 +1645,7 @@
       </c>
       <c r="C20" s="26">
         <f>ROUND(C4*0.4,0)*C9*12*0.15*3500</f>
-        <v>10080.000000000002</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="18" customHeight="1">
@@ -1701,7 +1690,7 @@
       </c>
       <c r="C25" s="34">
         <f>C22/C13</f>
-        <v>8.3333333333333329E-2</v>
+        <v>8.3333333333333301E-2</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="19.5" customHeight="1">
